--- a/SY Bsc Vedic Internal Marklist.xlsx
+++ b/SY Bsc Vedic Internal Marklist.xlsx
@@ -1,28 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\digam\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F142A0-4D43-4B34-B476-7D18E9C01F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BAED140-EF36-6B4C-B8AD-DE52FD640FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="30" windowWidth="23895" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>Roll No</t>
   </si>
@@ -267,9 +275,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -277,6 +286,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -587,781 +599,781 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="5"/>
-    <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9.14453125" style="7"/>
+    <col min="2" max="2" width="39.01171875" customWidth="1"/>
+    <col min="3" max="3" width="11.56640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.43359375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
         <v>501</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>9</v>
       </c>
-      <c r="D2" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="D2" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>502</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
         <v>503</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>7</v>
       </c>
-      <c r="D4" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>504</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>8</v>
       </c>
-      <c r="D5" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="D5" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>505</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="C6" s="5">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
         <v>506</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>9</v>
       </c>
-      <c r="D7" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="D7" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
         <v>507</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>508</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>5</v>
       </c>
-      <c r="D9" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="D9" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>509</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>4</v>
       </c>
-      <c r="D10" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="D10" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
         <v>510</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="4">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="C11" s="5">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>511</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>4</v>
       </c>
-      <c r="D12" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="D12" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
         <v>512</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>5</v>
       </c>
-      <c r="D13" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="D13" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>513</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>3</v>
       </c>
-      <c r="D14" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="D14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
         <v>514</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>3</v>
       </c>
-      <c r="D15" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="D15" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>515</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>5</v>
       </c>
-      <c r="D16" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="D16" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>516</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>6</v>
       </c>
-      <c r="D17" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="D17" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>517</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>4</v>
       </c>
-      <c r="D18" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="D18" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
         <v>518</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>3</v>
       </c>
-      <c r="D19" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="D19" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
         <v>519</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>2</v>
       </c>
-      <c r="D20" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="D20" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
         <v>520</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>4</v>
       </c>
-      <c r="D21" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="D21" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>521</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>7</v>
       </c>
-      <c r="D22" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="D22" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
         <v>522</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>9</v>
       </c>
-      <c r="D23" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="D23" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
         <v>523</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>7</v>
       </c>
-      <c r="D24" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="D24" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
         <v>524</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>7</v>
       </c>
-      <c r="D25" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="D25" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
         <v>525</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>6</v>
       </c>
-      <c r="D26" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="D26" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
         <v>526</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="C27" s="5">
+        <v>8</v>
+      </c>
+      <c r="D27" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
         <v>527</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>9</v>
       </c>
-      <c r="D28" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="D28" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
         <v>528</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>9</v>
       </c>
-      <c r="D29" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="D29" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
         <v>529</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>9</v>
       </c>
-      <c r="D30" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+      <c r="D30" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
         <v>530</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="4">
-        <v>10</v>
-      </c>
-      <c r="D31" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
+      <c r="C31" s="5">
+        <v>10</v>
+      </c>
+      <c r="D31" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
         <v>531</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>9</v>
       </c>
-      <c r="D32" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
+      <c r="D32" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
         <v>532</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <v>5</v>
       </c>
-      <c r="D33" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+      <c r="D33" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
         <v>533</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <v>8</v>
       </c>
-      <c r="D34" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+      <c r="D34" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
         <v>534</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="4">
-        <v>7</v>
-      </c>
-      <c r="D35" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="C35" s="5">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
         <v>535</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="5">
         <v>6</v>
       </c>
-      <c r="D36" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+      <c r="D36" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
         <v>536</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="5">
         <v>8</v>
       </c>
-      <c r="D37" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+      <c r="D37" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
         <v>537</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="5">
         <v>5</v>
       </c>
-      <c r="D38" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+      <c r="D38" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
         <v>538</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="5">
         <v>4</v>
       </c>
-      <c r="D39" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+      <c r="D39" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
         <v>539</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="5">
         <v>3</v>
       </c>
-      <c r="D40" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+      <c r="D40" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
         <v>540</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <v>3</v>
       </c>
-      <c r="D41" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+      <c r="D41" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
         <v>541</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="5">
         <v>9</v>
       </c>
-      <c r="D42" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+      <c r="D42" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
         <v>542</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="5">
         <v>2</v>
       </c>
-      <c r="D43" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+      <c r="D43" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
         <v>543</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="5">
         <v>4</v>
       </c>
-      <c r="D44" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+      <c r="D44" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
         <v>544</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <v>8</v>
       </c>
-      <c r="D45" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+      <c r="D45" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
         <v>545</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="5">
         <v>9</v>
       </c>
-      <c r="D46" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
+      <c r="D46" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="4">
         <v>546</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <v>4</v>
       </c>
-      <c r="D47" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
+      <c r="D47" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="4">
         <v>547</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <v>8</v>
       </c>
-      <c r="D48" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
+      <c r="D48" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
         <v>548</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="5">
         <v>2</v>
       </c>
-      <c r="D49" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
+      <c r="D49" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="4">
         <v>549</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="4">
-        <v>4</v>
-      </c>
-      <c r="D50" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
+      <c r="C50" s="5">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="4">
         <v>550</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
+      <c r="C51" s="5">
+        <v>6</v>
+      </c>
+      <c r="D51" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="4">
         <v>551</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D52" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
+      <c r="D52" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="4">
         <v>552</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>9</v>
       </c>
-      <c r="D53" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
+      <c r="D53" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="4">
         <v>553</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="5">
         <v>7</v>
       </c>
-      <c r="D54" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
+      <c r="D54" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="4">
         <v>554</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="5">
         <v>10</v>
       </c>
     </row>
@@ -1373,7 +1385,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1382,7 +1394,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SY Bsc Vedic Internal Marklist.xlsx
+++ b/SY Bsc Vedic Internal Marklist.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BAED140-EF36-6B4C-B8AD-DE52FD640FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB2DF451-D100-724D-9A17-59E4D8D19C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="30" windowWidth="23895" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,7 +979,7 @@
         <v>27</v>
       </c>
       <c r="C27" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="5">
         <v>10</v>
